--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_maternal_outcomes.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_maternal_outcomes.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1524,6 +1524,118 @@
       <c r="R17" t="inlineStr">
         <is>
           <t>Derived canonical birth weight (grams). Cleaning pipeline Module 15 computes coalesce(birthweight, bwt, bwtdis) -- three names for the same concept across Neotree form/script versions (bwtdis is birth weight despite its name; sources are identical where they overlap). Emitted in every dataset (NA where no source column is present). Originals retained. Use this column for low-birth-weight analysis. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Maternal age (years) -- canonical (derived)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>9</v>
+      </c>
+      <c r="Q18">
+        <v>60</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Derived canonical maternal age in years. Cleaning pipeline Module 15 computes coalesce(matageyrs, mat_age_date_years). ZIM captures matageyrs only (matagedate is a Malawi maternity-form field), so in ZIM data this column always equals matageyrs and mat_age_source is always 'matageyrs'; the shared derivation keeps the two countries on one schema. Emitted only where a source column is present. Originals retained. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2534,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D30">
@@ -2512,7 +2624,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D33">
@@ -2542,7 +2654,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D34">
@@ -4015,7 +4127,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4135,6 +4247,64 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Categorical with no value map entries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
